--- a/diseases/d110/1995-1999.xlsx
+++ b/diseases/d110/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25002,7 +25002,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25947,7 +25947,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26892,7 +26892,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27837,7 +27837,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28782,7 +28782,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -29727,7 +29727,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30672,7 +30672,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -31617,7 +31617,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32562,7 +32562,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -35081,7 +35081,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36026,7 +36026,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -36971,7 +36971,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37916,7 +37916,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39806,7 +39806,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -40751,7 +40751,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41696,7 +41696,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -42641,7 +42641,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43586,7 +43586,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -44531,7 +44531,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -52833,7 +52833,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54797,7 +54797,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -55742,7 +55742,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -56687,7 +56687,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -57632,7 +57632,7 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN294" t="b">
@@ -58577,7 +58577,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -59522,7 +59522,7 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN304" t="b">
@@ -60467,7 +60467,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -61412,7 +61412,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -62357,7 +62357,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -63302,7 +63302,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN324" t="b">
@@ -64247,7 +64247,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN329" t="b">

--- a/diseases/d110/1995-1999.xlsx
+++ b/diseases/d110/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21543,6 +21543,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22167,7 +22172,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22727,6 +22732,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23112,7 +23122,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23672,6 +23682,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24057,7 +24072,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24617,6 +24632,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25002,7 +25022,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25562,6 +25582,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25947,7 +25972,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26507,6 +26532,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26892,7 +26922,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27452,6 +27482,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27837,7 +27872,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28397,6 +28432,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28782,7 +28822,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -29342,6 +29382,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29727,7 +29772,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30287,6 +30332,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,7 +30722,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -31232,6 +31282,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31617,7 +31672,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32177,6 +32232,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32562,7 +32622,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -33512,6 +33572,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34136,7 +34201,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -34696,6 +34761,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35081,7 +35151,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35641,6 +35711,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36026,7 +36101,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -36586,6 +36661,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36971,7 +37051,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37531,6 +37611,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37916,7 +38001,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -38476,6 +38561,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38861,7 +38951,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39421,6 +39511,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39806,7 +39901,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -40366,6 +40461,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40751,7 +40851,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41311,6 +41411,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41696,7 +41801,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -42256,6 +42361,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42641,7 +42751,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43201,6 +43311,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43586,7 +43701,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -44146,6 +44261,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44531,7 +44651,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -49620,6 +49740,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52833,7 +52958,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54412,6 +54537,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54797,7 +54927,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -55357,6 +55487,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55742,7 +55877,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -56302,6 +56437,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56687,7 +56827,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -57247,6 +57387,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57632,7 +57777,7 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN294" t="b">
@@ -58192,6 +58337,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58577,7 +58727,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -59137,6 +59287,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59522,7 +59677,7 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN304" t="b">
@@ -60082,6 +60237,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60467,7 +60627,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -61027,6 +61187,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61412,7 +61577,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -61972,6 +62137,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62357,7 +62527,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -62917,6 +63087,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63302,7 +63477,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN324" t="b">
@@ -63862,6 +64037,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64247,7 +64427,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN329" t="b">

--- a/diseases/d110/1995-1999.xlsx
+++ b/diseases/d110/1995-1999.xlsx
@@ -46399,7 +46399,7 @@
         </is>
       </c>
       <c r="AT236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         </is>
       </c>
       <c r="AT237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>

--- a/diseases/d110/1995-1999.xlsx
+++ b/diseases/d110/1995-1999.xlsx
@@ -22164,11 +22164,6 @@
       <c r="O151" t="n">
         <v>6</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_MENI_ANNUAL</t>
@@ -22186,12 +22181,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -22201,11 +22191,6 @@
       </c>
       <c r="AT151" t="n">
         <v>1</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -22271,17 +22256,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -22306,112 +22291,29 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O152" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_MENI_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_MENI_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>Invasive meningococcal disease</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN152" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -22420,65 +22322,55 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_MENI_ANNUAL</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT152" t="n">
         <v>1</v>
       </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22510,12 +22402,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -22549,15 +22441,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>9</v>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
@@ -22566,7 +22456,7 @@
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
@@ -22574,52 +22464,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -22651,12 +22537,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -22690,13 +22576,15 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
@@ -22705,7 +22593,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
@@ -22713,48 +22601,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS154" t="inlineStr"/>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22786,12 +22678,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -22816,23 +22708,23 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O155" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -22852,7 +22744,7 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -22860,42 +22752,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22927,12 +22819,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -22966,15 +22858,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>5</v>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
@@ -22983,7 +22873,7 @@
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
@@ -22991,52 +22881,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23068,12 +22954,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -23107,13 +22993,15 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
@@ -23122,7 +23010,7 @@
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
@@ -23130,48 +23018,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS157" t="inlineStr"/>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23203,12 +23095,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -23233,23 +23125,23 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N158" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O158" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -23269,7 +23161,7 @@
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT158" t="n">
@@ -23277,42 +23169,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23344,12 +23236,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -23383,15 +23275,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>3</v>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
@@ -23400,7 +23290,7 @@
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
@@ -23408,52 +23298,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23485,12 +23371,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -23524,71 +23410,77 @@
         </is>
       </c>
       <c r="N160" t="n">
+        <v>3</v>
+      </c>
+      <c r="O160" t="n">
+        <v>3</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT160" t="n">
         <v>1</v>
       </c>
-      <c r="O160" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP160" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
-      <c r="AT160" t="n">
-        <v>0</v>
-      </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23620,12 +23512,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -23650,23 +23542,23 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O161" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -23686,7 +23578,7 @@
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT161" t="n">
@@ -23694,42 +23586,42 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23761,12 +23653,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -23800,15 +23692,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>7</v>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
@@ -23817,7 +23707,7 @@
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
@@ -23825,52 +23715,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23902,12 +23788,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -23941,71 +23827,77 @@
         </is>
       </c>
       <c r="N163" t="n">
+        <v>7</v>
+      </c>
+      <c r="O163" t="n">
+        <v>7</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
         <v>1</v>
       </c>
-      <c r="O163" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
-      <c r="AT163" t="n">
-        <v>0</v>
-      </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24037,12 +23929,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -24067,23 +23959,23 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O164" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -24103,7 +23995,7 @@
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -24111,42 +24003,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24178,12 +24070,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -24217,15 +24109,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>8</v>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
@@ -24234,7 +24124,7 @@
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
@@ -24242,52 +24132,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24319,12 +24205,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -24358,13 +24244,15 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
@@ -24373,7 +24261,7 @@
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
@@ -24381,48 +24269,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS166" t="inlineStr"/>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24454,12 +24346,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -24484,23 +24376,23 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -24520,7 +24412,7 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT167" t="n">
@@ -24528,42 +24420,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24595,12 +24487,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -24634,15 +24526,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>1</v>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
@@ -24651,7 +24541,7 @@
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
@@ -24659,52 +24549,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24736,12 +24622,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -24775,13 +24661,15 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
@@ -24790,7 +24678,7 @@
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
@@ -24798,48 +24686,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS169" t="inlineStr"/>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24871,12 +24763,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -24901,12 +24793,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N170" t="n">
@@ -24917,7 +24809,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -24937,7 +24829,7 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT170" t="n">
@@ -24945,42 +24837,42 @@
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25012,12 +24904,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -25051,15 +24943,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>5</v>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
@@ -25068,7 +24958,7 @@
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
@@ -25076,52 +24966,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25153,12 +25039,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -25192,13 +25078,15 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
@@ -25207,7 +25095,7 @@
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
@@ -25215,48 +25103,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS172" t="inlineStr"/>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25288,12 +25180,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -25318,23 +25210,23 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O173" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -25354,7 +25246,7 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT173" t="n">
@@ -25362,42 +25254,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25429,12 +25321,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -25468,15 +25360,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
-        <v>2</v>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
@@ -25485,7 +25375,7 @@
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
@@ -25493,52 +25383,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25570,12 +25456,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -25609,13 +25495,15 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O175" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q175" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
@@ -25624,7 +25512,7 @@
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
@@ -25632,48 +25520,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS175" t="inlineStr"/>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25705,12 +25597,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -25735,23 +25627,23 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O176" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -25771,7 +25663,7 @@
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT176" t="n">
@@ -25779,42 +25671,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25846,12 +25738,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -25885,15 +25777,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>2</v>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
@@ -25902,7 +25792,7 @@
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
@@ -25910,52 +25800,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25987,12 +25873,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -26026,13 +25912,15 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
@@ -26041,7 +25929,7 @@
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
@@ -26049,48 +25937,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS178" t="inlineStr"/>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26122,12 +26014,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -26152,12 +26044,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-11-01</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="N179" t="n">
@@ -26168,7 +26060,7 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -26188,7 +26080,7 @@
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT179" t="n">
@@ -26196,42 +26088,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26263,12 +26155,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -26302,15 +26194,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>5</v>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
@@ -26319,7 +26209,7 @@
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
@@ -26327,52 +26217,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26404,12 +26290,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -26443,13 +26329,15 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
@@ -26458,7 +26346,7 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
@@ -26466,48 +26354,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS181" t="inlineStr"/>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26539,12 +26431,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -26569,23 +26461,23 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-12-01</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-12</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O182" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -26605,7 +26497,7 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -26613,42 +26505,42 @@
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26680,12 +26572,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -26719,15 +26611,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
-        <v>2</v>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0</v>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
@@ -26736,7 +26626,7 @@
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
@@ -26744,52 +26634,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+      <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26821,12 +26707,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -26860,13 +26746,15 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
@@ -26875,7 +26763,7 @@
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
@@ -26883,187 +26771,50 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS184" t="inlineStr"/>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>D110</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>meningococcal-disease</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Meningococcal disease</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>D110</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Meningococcal disease</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>脑膜炎球菌病</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>1999-12-01</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>1999-12</t>
-        </is>
-      </c>
-      <c r="N185" t="n">
-        <v>8</v>
-      </c>
-      <c r="O185" t="n">
-        <v>8</v>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP185" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT185" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV185" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW185" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX185" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY185" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ185" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA185" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB185" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC185" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -27195,7 +26946,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -27215,7 +26966,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -27225,7 +26976,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d110/1995-1999.xlsx
+++ b/diseases/d110/1995-1999.xlsx
@@ -21538,6 +21538,11 @@
       <c r="Q106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21550,13 +21555,23 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22712,6 +22727,11 @@
       <c r="Q112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22724,13 +22744,23 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23647,6 +23677,11 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23659,13 +23694,23 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24582,6 +24627,11 @@
       <c r="Q122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24594,13 +24644,23 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
       </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV122" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25517,6 +25577,11 @@
       <c r="Q127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25529,13 +25594,23 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
       </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV127" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26452,6 +26527,11 @@
       <c r="Q132" t="n">
         <v>0</v>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26464,13 +26544,23 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
       </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV132" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27387,6 +27477,11 @@
       <c r="Q137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27399,13 +27494,23 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28322,6 +28427,11 @@
       <c r="Q142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28334,13 +28444,23 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
       </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV142" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29257,6 +29377,11 @@
       <c r="Q147" t="n">
         <v>0</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29269,13 +29394,23 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
       </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV147" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30192,6 +30327,11 @@
       <c r="Q152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30204,13 +30344,23 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
       </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV152" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31127,6 +31277,11 @@
       <c r="Q157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31139,13 +31294,23 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
       </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV157" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32062,6 +32227,11 @@
       <c r="Q162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32074,13 +32244,23 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
       </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV162" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33387,6 +33567,11 @@
       <c r="Q169" t="n">
         <v>0</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33399,13 +33584,23 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
       </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV169" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34561,6 +34756,11 @@
       <c r="Q175" t="n">
         <v>0</v>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34573,13 +34773,23 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
       </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV175" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -35496,6 +35706,11 @@
       <c r="Q180" t="n">
         <v>0</v>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35508,13 +35723,23 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
       </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV180" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -36431,6 +36656,11 @@
       <c r="Q185" t="n">
         <v>0</v>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36443,13 +36673,23 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
       </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV185" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37366,6 +37606,11 @@
       <c r="Q190" t="n">
         <v>0</v>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37378,13 +37623,23 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
       </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV190" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38301,6 +38556,11 @@
       <c r="Q195" t="n">
         <v>0</v>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38313,13 +38573,23 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
       </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV195" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39236,6 +39506,11 @@
       <c r="Q200" t="n">
         <v>0</v>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39248,13 +39523,23 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
       </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV200" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -40171,6 +40456,11 @@
       <c r="Q205" t="n">
         <v>0</v>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40183,13 +40473,23 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
       </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV205" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41106,6 +41406,11 @@
       <c r="Q210" t="n">
         <v>0</v>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41118,13 +41423,23 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
       </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV210" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42041,6 +42356,11 @@
       <c r="Q215" t="n">
         <v>0</v>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42053,13 +42373,23 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
       </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV215" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42976,6 +43306,11 @@
       <c r="Q220" t="n">
         <v>0</v>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42988,13 +43323,23 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
         <v>0</v>
       </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV220" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43911,6 +44256,11 @@
       <c r="Q225" t="n">
         <v>0</v>
       </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43923,13 +44273,23 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
         <v>0</v>
       </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV225" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -49224,6 +49584,11 @@
       <c r="Q252" t="n">
         <v>0</v>
       </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49236,13 +49601,23 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
       </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV252" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -53616,6 +53991,11 @@
       <c r="Q274" t="n">
         <v>0</v>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53628,13 +54008,23 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
         <v>0</v>
       </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV274" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -54551,6 +54941,11 @@
       <c r="Q279" t="n">
         <v>0</v>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54563,13 +54958,23 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr"/>
       <c r="AT279" t="n">
         <v>0</v>
       </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV279" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -55486,6 +55891,11 @@
       <c r="Q284" t="n">
         <v>0</v>
       </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -55498,13 +55908,23 @@
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS284" t="inlineStr"/>
       <c r="AT284" t="n">
         <v>0</v>
       </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV284" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -56421,6 +56841,11 @@
       <c r="Q289" t="n">
         <v>0</v>
       </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA289" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -56433,13 +56858,23 @@
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS289" t="inlineStr"/>
       <c r="AT289" t="n">
         <v>0</v>
       </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV289" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -57356,6 +57791,11 @@
       <c r="Q294" t="n">
         <v>0</v>
       </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA294" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57368,13 +57808,23 @@
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr"/>
       <c r="AT294" t="n">
         <v>0</v>
       </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV294" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -58291,6 +58741,11 @@
       <c r="Q299" t="n">
         <v>0</v>
       </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58303,13 +58758,23 @@
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr"/>
       <c r="AT299" t="n">
         <v>0</v>
       </c>
+      <c r="AU299" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV299" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -59226,6 +59691,11 @@
       <c r="Q304" t="n">
         <v>0</v>
       </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA304" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -59238,13 +59708,23 @@
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR304" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS304" t="inlineStr"/>
       <c r="AT304" t="n">
         <v>0</v>
       </c>
+      <c r="AU304" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV304" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -60161,6 +60641,11 @@
       <c r="Q309" t="n">
         <v>0</v>
       </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60173,13 +60658,23 @@
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR309" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS309" t="inlineStr"/>
       <c r="AT309" t="n">
         <v>0</v>
       </c>
+      <c r="AU309" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV309" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -61096,6 +61591,11 @@
       <c r="Q314" t="n">
         <v>0</v>
       </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA314" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61108,13 +61608,23 @@
       </c>
       <c r="AP314" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR314" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS314" t="inlineStr"/>
       <c r="AT314" t="n">
         <v>0</v>
       </c>
+      <c r="AU314" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV314" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -62031,6 +62541,11 @@
       <c r="Q319" t="n">
         <v>0</v>
       </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA319" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62043,13 +62558,23 @@
       </c>
       <c r="AP319" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS319" t="inlineStr"/>
       <c r="AT319" t="n">
         <v>0</v>
       </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV319" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -62966,6 +63491,11 @@
       <c r="Q324" t="n">
         <v>0</v>
       </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA324" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62978,12 +63508,22 @@
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR324" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS324" t="inlineStr"/>
       <c r="AT324" t="n">
         <v>0</v>
+      </c>
+      <c r="AU324" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV324" t="inlineStr">
         <is>
